--- a/01_Input/00_CO Validation/Indonesia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Indonesia - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="245" documentId="11_5E2291AF6514A09EC6E1AA69F27A1135B06B1CFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F5307E3-5F08-4DA3-AE4B-1CB1983247E4}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="11_5E2291AF6514A09EC6E1AA69F27A1135B06B1CFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E6BB48B-BD8C-4C26-BCDE-AAD843FD7150}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,6 +15,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="115">
   <si>
     <t>Project ID</t>
   </si>
@@ -208,7 +211,7 @@
     <t>PIMS+</t>
   </si>
   <si>
-    <t>Other Energy Services</t>
+    <t>Transport Services</t>
   </si>
   <si>
     <t>Number of direct project beneficiaries disaggregated by gender (individual people) [GEF core indicator]</t>
@@ -272,6 +275,9 @@
   </si>
   <si>
     <t>0</t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
   </si>
   <si>
     <t>Commensts</t>
@@ -544,7 +550,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -619,6 +625,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -627,7 +679,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -668,6 +720,75 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -706,42 +827,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1058,349 +1143,351 @@
     <col min="6" max="6" width="64.7109375" style="6" customWidth="1"/>
     <col min="7" max="8" width="36.7109375" style="6" customWidth="1"/>
     <col min="9" max="9" width="32.7109375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="6"/>
+    <col min="10" max="14" width="9.140625" style="6"/>
+    <col min="15" max="15" width="11.42578125" style="6" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="45.75">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="L1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="M1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="P1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="Q1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="R1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="S1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="13"/>
     </row>
     <row r="2" spans="1:20" ht="72.75" customHeight="1">
-      <c r="A2" s="31">
+      <c r="A2" s="37">
         <v>126434</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="31">
+      <c r="D2" s="18">
         <v>15028509</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="33">
+      <c r="G2" s="19">
         <v>0</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36" t="s">
+      <c r="K2" s="22"/>
+      <c r="L2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36" t="s">
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="36" t="s">
+      <c r="P2" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
     </row>
     <row r="3" spans="1:20" ht="60.75">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="33" t="s">
+      <c r="C3" s="33"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="19">
         <v>0</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="19">
         <v>50</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="35"/>
-      <c r="K3" s="38">
+      <c r="J3" s="21"/>
+      <c r="K3" s="24">
         <v>0.3</v>
       </c>
-      <c r="L3" s="36" t="s">
+      <c r="L3" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36" t="s">
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="36" t="s">
+      <c r="P3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
     </row>
     <row r="4" spans="1:20" ht="60.75">
       <c r="A4" s="31"/>
       <c r="B4" s="31"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="33" t="s">
+      <c r="C4" s="33"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="19">
         <v>0</v>
       </c>
-      <c r="H4" s="37">
+      <c r="H4" s="23">
         <v>21</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="35"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36" t="s">
+      <c r="J4" s="21"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36" t="s">
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="36" t="s">
+      <c r="P4" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
     </row>
     <row r="5" spans="1:20" ht="60.75">
       <c r="A5" s="31"/>
       <c r="B5" s="31"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="33" t="s">
+      <c r="C5" s="33"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="23">
         <v>0</v>
       </c>
-      <c r="H5" s="37">
+      <c r="H5" s="23">
         <v>600</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="35"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36" t="s">
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P5" s="36" t="s">
+      <c r="P5" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
     </row>
     <row r="6" spans="1:20" ht="60.75">
-      <c r="A6" s="31">
+      <c r="A6" s="37">
         <v>142434</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="18">
         <v>1796132</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="23">
         <v>0</v>
       </c>
-      <c r="H6" s="33">
+      <c r="H6" s="19">
         <v>10</v>
       </c>
-      <c r="I6" s="33"/>
-      <c r="J6" s="31" t="s">
+      <c r="I6" s="19"/>
+      <c r="J6" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36" t="s">
+      <c r="K6" s="22"/>
+      <c r="L6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36" t="s">
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P6" s="36" t="s">
+      <c r="P6" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
     </row>
     <row r="7" spans="1:20" ht="60.75">
       <c r="A7" s="31"/>
       <c r="B7" s="31"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="33" t="s">
+      <c r="C7" s="33"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="23">
         <v>0</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="23">
         <v>329</v>
       </c>
-      <c r="I7" s="33"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36" t="s">
+      <c r="I7" s="19"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36" t="s">
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P7" s="36" t="s">
+      <c r="P7" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36" t="s">
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="S7" s="36" t="s">
+      <c r="S7" s="22" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="60.75">
-      <c r="A8" s="31"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="33" t="s">
+      <c r="A8" s="32"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="23">
         <v>0</v>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="23">
         <v>350</v>
       </c>
-      <c r="I8" s="33"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36" t="s">
+      <c r="I8" s="19"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36" t="s">
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P8" s="36" t="s">
+      <c r="P8" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="36"/>
-    </row>
-    <row r="9" spans="1:20" ht="60.75">
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+    </row>
+    <row r="9" spans="1:20" ht="45.75">
       <c r="A9" s="36">
         <v>6333</v>
       </c>
@@ -1413,170 +1500,170 @@
       <c r="D9" s="36">
         <v>1816500</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="39">
+      <c r="H9" s="25">
         <v>643224</v>
       </c>
-      <c r="I9" s="33"/>
-      <c r="J9" s="36" t="s">
+      <c r="I9" s="19"/>
+      <c r="J9" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9" s="24">
         <v>0.24</v>
       </c>
-      <c r="L9" s="36" t="s">
+      <c r="L9" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36" t="s">
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P9" s="36" t="s">
+      <c r="P9" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
     </row>
     <row r="10" spans="1:20" ht="91.5">
-      <c r="A10" s="31">
+      <c r="A10" s="37">
         <v>5721</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="18">
         <v>2633372</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="33" t="s">
+      <c r="F10" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="19">
         <v>125</v>
       </c>
-      <c r="I10" s="33"/>
-      <c r="J10" s="31" t="s">
+      <c r="I10" s="19"/>
+      <c r="J10" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="24">
         <v>0.34</v>
       </c>
-      <c r="L10" s="36" t="s">
+      <c r="L10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36" t="s">
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P10" s="36" t="s">
+      <c r="P10" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="36"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="22"/>
     </row>
     <row r="11" spans="1:20" ht="60.75">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="33" t="s">
+      <c r="A11" s="32"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="26">
         <v>6</v>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="19">
         <v>10</v>
       </c>
-      <c r="I11" s="33" t="s">
+      <c r="I11" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="31"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36" t="s">
+      <c r="J11" s="18"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36" t="s">
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P11" s="36" t="s">
+      <c r="P11" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
     </row>
     <row r="12" spans="1:20" ht="60.75">
-      <c r="A12" s="36">
+      <c r="A12" s="35">
         <v>4673</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="35">
         <v>8025000</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="F12" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="37" t="s">
+      <c r="G12" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="33" t="s">
+      <c r="I12" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="36" t="s">
+      <c r="J12" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36" t="s">
+      <c r="K12" s="22"/>
+      <c r="L12" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36" t="s">
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="P12" s="36" t="s">
+      <c r="P12" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="36"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="9"/>
@@ -1691,16 +1778,16 @@
       <c r="T1" s="13"/>
     </row>
     <row r="2" spans="1:20" ht="72.75" customHeight="1">
-      <c r="A2" s="16">
+      <c r="A2" s="39">
         <v>126434</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="39">
         <v>15028509</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -1718,7 +1805,7 @@
       <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="41" t="s">
         <v>25</v>
       </c>
       <c r="L2" s="6" t="s">
@@ -1732,10 +1819,10 @@
       </c>
     </row>
     <row r="3" spans="1:20" ht="60.75">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="21"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="44"/>
       <c r="E3" s="4" t="s">
         <v>28</v>
       </c>
@@ -1751,7 +1838,7 @@
       <c r="I3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="19"/>
+      <c r="J3" s="42"/>
       <c r="K3" s="14">
         <v>0.3</v>
       </c>
@@ -1766,10 +1853,10 @@
       </c>
     </row>
     <row r="4" spans="1:20" ht="60.75">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="21"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="44"/>
       <c r="E4" s="4" t="s">
         <v>31</v>
       </c>
@@ -1785,7 +1872,7 @@
       <c r="I4" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="J4" s="19"/>
+      <c r="J4" s="42"/>
       <c r="L4" s="6" t="s">
         <v>26</v>
       </c>
@@ -1797,10 +1884,10 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="60.75">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="17"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="4" t="s">
         <v>34</v>
       </c>
@@ -1816,7 +1903,7 @@
       <c r="I5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="20"/>
+      <c r="J5" s="43"/>
       <c r="L5" s="6" t="s">
         <v>26</v>
       </c>
@@ -1828,16 +1915,16 @@
       </c>
     </row>
     <row r="6" spans="1:20" ht="60.75">
-      <c r="A6" s="16">
+      <c r="A6" s="39">
         <v>142434</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="39">
         <v>1796132</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -1853,7 +1940,7 @@
         <v>10</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="39" t="s">
         <v>40</v>
       </c>
       <c r="L6" s="6" t="s">
@@ -1867,10 +1954,10 @@
       </c>
     </row>
     <row r="7" spans="1:20" ht="60.75">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="21"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="44"/>
       <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
@@ -1884,7 +1971,7 @@
         <v>329</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="21"/>
+      <c r="J7" s="44"/>
       <c r="L7" s="6" t="s">
         <v>26</v>
       </c>
@@ -1902,10 +1989,10 @@
       </c>
     </row>
     <row r="8" spans="1:20" ht="60.75">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="17"/>
+      <c r="A8" s="40"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="40"/>
       <c r="E8" s="4" t="s">
         <v>28</v>
       </c>
@@ -1919,7 +2006,7 @@
         <v>350</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="17"/>
+      <c r="J8" s="40"/>
       <c r="L8" s="6" t="s">
         <v>26</v>
       </c>
@@ -1944,7 +2031,7 @@
         <v>1816500</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>50</v>
@@ -1971,16 +2058,16 @@
       </c>
     </row>
     <row r="10" spans="1:20" ht="91.5">
-      <c r="A10" s="16">
+      <c r="A10" s="39">
         <v>5721</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="39">
         <v>2633372</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -1996,7 +2083,7 @@
         <v>125</v>
       </c>
       <c r="I10" s="4"/>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="39" t="s">
         <v>51</v>
       </c>
       <c r="K10" s="14">
@@ -2013,10 +2100,10 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="60.75">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
       <c r="E11" s="4" t="s">
         <v>31</v>
       </c>
@@ -2030,7 +2117,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="4"/>
-      <c r="J11" s="17"/>
+      <c r="J11" s="40"/>
       <c r="L11" s="6" t="s">
         <v>52</v>
       </c>
@@ -2188,23 +2275,23 @@
         <v>8</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="72.75" customHeight="1">
-      <c r="A2" s="16">
+      <c r="A2" s="39">
         <v>126434</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="39">
         <v>15028509</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="41" t="s">
         <v>25</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -2217,21 +2304,21 @@
         <v>63</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.75">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="19"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="42"/>
       <c r="F3" s="4" t="s">
         <v>28</v>
       </c>
@@ -2242,18 +2329,18 @@
         <v>65</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30.75">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="19"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="42"/>
       <c r="F4" s="4" t="s">
         <v>31</v>
       </c>
@@ -2264,18 +2351,18 @@
         <v>66</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45.75">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="20"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="43"/>
       <c r="F5" s="4" t="s">
         <v>34</v>
       </c>
@@ -2286,26 +2373,26 @@
         <v>68</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="45.75">
-      <c r="A6" s="16">
+      <c r="A6" s="39">
         <v>142434</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="39">
         <v>1796132</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="39" t="s">
         <v>40</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2318,18 +2405,18 @@
         <v>68</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
       <c r="F7" s="4" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>43</v>
@@ -2338,16 +2425,16 @@
         <v>68</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="A8" s="40"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
       <c r="F8" s="4" t="s">
         <v>28</v>
       </c>
@@ -2358,7 +2445,7 @@
         <v>68</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J8" s="4"/>
     </row>
@@ -2379,33 +2466,33 @@
         <v>51</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>50</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:11" ht="91.5">
-      <c r="A10" s="16">
+      <c r="A10" s="39">
         <v>5721</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="39">
         <v>2633372</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="39" t="s">
         <v>51</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -2418,16 +2505,16 @@
         <v>55</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="45.75">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
       <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
@@ -2438,7 +2525,7 @@
         <v>57</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" s="4"/>
     </row>
@@ -2468,7 +2555,7 @@
         <v>60</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>62</v>
@@ -2479,21 +2566,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="E2:E5"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2525,160 +2612,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="25" t="s">
-        <v>86</v>
+      <c r="A2" s="48" t="s">
+        <v>87</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="25"/>
+      <c r="A3" s="48"/>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="25"/>
+      <c r="A4" s="48"/>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="26" t="s">
-        <v>92</v>
+      <c r="A5" s="49" t="s">
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="26"/>
+      <c r="A6" s="49"/>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="26"/>
+      <c r="A7" s="49"/>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="26"/>
+      <c r="A8" s="49"/>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="26"/>
+      <c r="A9" s="49"/>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="27" t="s">
-        <v>102</v>
+      <c r="A10" s="50" t="s">
+        <v>103</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="27"/>
+      <c r="A11" s="50"/>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="28" t="s">
-        <v>106</v>
+      <c r="A12" s="51" t="s">
+        <v>107</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="28"/>
+      <c r="A13" s="51"/>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="28"/>
+      <c r="A14" s="51"/>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2693,12 +2780,36 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Verania Andria</DisplayName>
+        <AccountId>1156</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Sujala Pant</DisplayName>
+        <AccountId>1225</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Akiko Yamamoto</DisplayName>
+        <AccountId>84</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2951,40 +3062,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Verania Andria</DisplayName>
-        <AccountId>1156</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Sujala Pant</DisplayName>
-        <AccountId>1225</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Akiko Yamamoto</DisplayName>
-        <AccountId>84</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2D7830B-D252-4AE4-BDBD-976B65B8A87C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2031F88-137D-4398-9974-44E9D22D0D48}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2992,5 +3079,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2031F88-137D-4398-9974-44E9D22D0D48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2D7830B-D252-4AE4-BDBD-976B65B8A87C}"/>
 </file>
--- a/01_Input/00_CO Validation/Indonesia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Indonesia - Energy Projects.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28619"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="318" documentId="11_5E2291AF6514A09EC6E1AA69F27A1135B06B1CFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{872B48C5-8B0C-4B7E-8C1F-809592203260}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="792" documentId="11_5E2291AF6514A09EC6E1AA69F27A1135B06B1CFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8045291-9093-43BE-A1C7-AD3DC54BC71C}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -33,8 +38,53 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={8D1850B6-7295-40DA-83A4-1A6D64245AA8}</author>
+    <author>tc={8CCC4E43-5BC1-43AE-8F36-8B20E99C45BE}</author>
+    <author>tc={74C36888-33F0-4E51-8559-FC66D10B7C5A}</author>
+    <author>tc={E195C2DF-08F3-4FAE-AE76-17FBF46E5A37}</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{8D1850B6-7295-40DA-83A4-1A6D64245AA8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    @Mathilde Sari Gokmauli @Sugiyanto Sugiyanto Please update data for ACCESS. Feel free to include relevant indicators that have not been reflected here</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="1" shapeId="0" xr:uid="{8CCC4E43-5BC1-43AE-8F36-8B20E99C45BE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    @Heri Tabadepu @Dzul Afifah Arifin Can you update the information here for the Carbon Pricing Project? Feel free to add relevant indicators not captured here</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="2" shapeId="0" xr:uid="{74C36888-33F0-4E51-8559-FC66D10B7C5A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    @Heri Tabadepu Can you review details for MTRE3 and add/update as necessary?</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="3" shapeId="0" xr:uid="{E195C2DF-08F3-4FAE-AE76-17FBF46E5A37}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    @Heri Tabadepu @Dzul Afifah Arifin Can you help populate data for this project? </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="218">
   <si>
     <t>Project ID</t>
   </si>
@@ -99,13 +149,446 @@
     <t>Policy Population</t>
   </si>
   <si>
+    <t>Accelerating Clean Energy Access to Reduce Inequality (ACCESS)</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00126434</t>
+  </si>
+  <si>
+    <t>Electricity Access</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Number of households in targeted villages getting electricity supply generated </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>from 23 solar PV off-grid power plants (total 1.2 MewaWatt capacity) constructed by project fund</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> (disaggregated by gender) </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">3025 HH
+</t>
+  </si>
+  <si>
+    <t>The construction of solar power plant is completed in all locations providing electricity access to 3,449 households</t>
+  </si>
+  <si>
+    <t>KOICA</t>
+  </si>
+  <si>
+    <t>Non-VF</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount of generated electricity per month </t>
+  </si>
+  <si>
+    <t>123 kWh</t>
+  </si>
+  <si>
+    <t>Achieved - Amount generated electricity 34,668 kWh</t>
+  </si>
+  <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t>Numbers of local people trained in field training on operation &amp; maintenance and passed post-test (disaggregated by gender).</t>
+  </si>
+  <si>
+    <t>achieved – 70 (46% women)</t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t>Establishment of village electricity enterprise (BUMDES Listrik Desa) or Renewable Energy Service Cooperative (RESCO).</t>
+  </si>
+  <si>
+    <t>achieved – 21 village enterprise have been established or renewed</t>
+  </si>
+  <si>
+    <t>Campaign Participant</t>
+  </si>
+  <si>
+    <t>Number of participants from stakeholder's institutions (government, private, donors, NGOs, regional development banks) receiving dissemination products, cumulative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achieved - 1067 people have been engaged </t>
+  </si>
+  <si>
+    <t>Small Enterprises</t>
+  </si>
+  <si>
+    <t>Number of women led businesses in the villages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 women led business have been assisted to grow the business </t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>total capacity of the power plants</t>
+  </si>
+  <si>
+    <t>1.1 MW (duplicate)</t>
+  </si>
+  <si>
+    <t>achieved - total capacity of the 22 power plants is around 1,1 MWp</t>
+  </si>
+  <si>
+    <t>Energy Infrastructure Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number of power plant constructed </t>
+  </si>
+  <si>
+    <t>achieved - 22 power plants are operational</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>*add indicator on GHG emission reduced/avoided</t>
+  </si>
+  <si>
+    <t>PIP Accelerating Robust Carbon Pricing</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00142434</t>
+  </si>
+  <si>
+    <t>govt staffs certified as emission reduction verifiers</t>
+  </si>
+  <si>
+    <t>JSB</t>
+  </si>
+  <si>
+    <t>Accelerating just energy transition</t>
+  </si>
+  <si>
+    <t>mitigation actions registered in national registry system</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>NDC Support</t>
+  </si>
+  <si>
+    <t>Decarbonization</t>
+  </si>
+  <si>
+    <t>National</t>
+  </si>
+  <si>
+    <t>#people being involved in capacity building and policy dialogue</t>
+  </si>
+  <si>
+    <t>Electric Vehicles in Indonesia (ENTREV)</t>
+  </si>
+  <si>
+    <t>https://co.pims.undp.org/project/view?id=6333</t>
+  </si>
+  <si>
+    <t>Transportation and E-mobility Services</t>
+  </si>
+  <si>
+    <t>Number of direct project beneficiaries disaggregated by gender (individual people) [GEF core indicator]</t>
+  </si>
+  <si>
+    <t>GEF</t>
+  </si>
+  <si>
+    <t>VF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financing support </t>
+  </si>
+  <si>
+    <t>Volume of investment mobilized and leveraged for low GHG development</t>
+  </si>
+  <si>
+    <t>at least $ 13.4 million</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achievement (as of May 2024): $2,121,624  </t>
+  </si>
+  <si>
+    <t>Number of direct project beneficiaries from the EV infrastructure intervention, disaggregated by gender (individual people)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achievement (as of May 2024): total of 163,967 beneficiaries, including 12,017 women. </t>
+  </si>
+  <si>
+    <t>GHG emissions reduction/avoided</t>
+  </si>
+  <si>
+    <t>473.8 ktCO2</t>
+  </si>
+  <si>
+    <t>Achievement (as of May 2024): 
+a) Direct ER : 14.3 ktCO2
+b) Secondary direct ER : 153.13 ktCO2
+c) Indirect ER : 6,123.1 ktCO2
+Direct emission reduction (ER) from GEF-funded pilot activities
+Secondary direct from co-financed interventions
+Indirect emission reduction through various interventions, including policies
+GHG calculations will be verified during the midterm review in 2025"</t>
+  </si>
+  <si>
+    <t>ADLIGHT</t>
+  </si>
+  <si>
+    <t>https://co.pims.undp.org/project/view?id=5721</t>
+  </si>
+  <si>
+    <t>Cumulative number of lighting manufacturers who received technical assistance to upgrade production facilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achievement: 10 </t>
+  </si>
+  <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
+    <t>To increase the penetration of high quality energy efficient lighting technologies in  Indonesia through the transformation of the national market</t>
+  </si>
+  <si>
+    <t>77.45 GWh</t>
+  </si>
+  <si>
+    <t>Achievement: 74.33 GWh</t>
+  </si>
+  <si>
+    <t>62.58 ktCO2e</t>
+  </si>
+  <si>
+    <t>Achievement: 75.16 ktCO2e</t>
+  </si>
+  <si>
+    <t>Number of women and men participating in capacity building trainings throughout the project</t>
+  </si>
+  <si>
+    <t>60/140 (w/m)</t>
+  </si>
+  <si>
+    <t>Achievement: 103 women, 149 men</t>
+  </si>
+  <si>
+    <t>RE Market Transformation (NAMA)</t>
+  </si>
+  <si>
+    <t>https://co.pims.undp.org/project/view?id=4673</t>
+  </si>
+  <si>
+    <t>Cumulative number of additional households (from baseline) having access to electricity in pilot provinces</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>320000 HH</t>
+  </si>
+  <si>
+    <t>Achievement: 327667 HH</t>
+  </si>
+  <si>
+    <t>Cumulative capacity of RE investment projects implemented</t>
+  </si>
+  <si>
+    <t>15 MW (duplicate)</t>
+  </si>
+  <si>
+    <t>Achievement: 30.72 MW</t>
+  </si>
+  <si>
+    <t>Cumulative energy saved from EE in commercial buildings, facilitated by project, MWh</t>
+  </si>
+  <si>
+    <t>8,550 MWh</t>
+  </si>
+  <si>
+    <t>Achievement: 248,952 MWh</t>
+  </si>
+  <si>
+    <t>Market Intervention</t>
+  </si>
+  <si>
+    <t>Cumulative volume of public and private investment mobilized by the SEF, US$ million</t>
+  </si>
+  <si>
+    <t>US$ 25 million</t>
+  </si>
+  <si>
+    <t>Achievement: US$ 57.77 million</t>
+  </si>
+  <si>
+    <t>Scale up energy finance</t>
+  </si>
+  <si>
+    <t>Number of small to medium scale RE/EE projects that were financially supported by Sustainable Energy Fund</t>
+  </si>
+  <si>
+    <t>10 small-medium RE/EE projects</t>
+  </si>
+  <si>
+    <t>Achievement: 11 small-medium RE/EE projects</t>
+  </si>
+  <si>
+    <t>27029 tCO2e</t>
+  </si>
+  <si>
+    <t>Achievement 217509 tCO2e</t>
+  </si>
+  <si>
+    <t>01000330</t>
+  </si>
+  <si>
+    <t>PIP JSB Advancing Indonesia's NDC Targets in the Energy Sector</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/01000330</t>
+  </si>
+  <si>
+    <t>Number of people trained/educated/informed 
+through technical transfers, dialogues, 
+workshops, campaigns, and other efforts 
+(disaggregated by: male, female, youth (15-24) 
+and indigenous people)</t>
+  </si>
+  <si>
+    <t>Achievement 3,726 individuals</t>
+  </si>
+  <si>
+    <t>38,3%</t>
+  </si>
+  <si>
+    <t>Government Capacity-Building</t>
+  </si>
+  <si>
+    <t>Digital &amp; Data</t>
+  </si>
+  <si>
+    <t>01000743</t>
+  </si>
+  <si>
+    <t>PIP Just Energy Transition</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/01000743</t>
+  </si>
+  <si>
+    <t>Establishment of Just Transition framework within the Indonesia Just Energy Transition Partnership (JETP) Comprehensive Investment and Policy Plan (CIPP) document</t>
+  </si>
+  <si>
+    <t>1 document</t>
+  </si>
+  <si>
+    <t>In November 2023, the Government of Indonesia launched the JETP CIPP document</t>
+  </si>
+  <si>
+    <t>01002479</t>
+  </si>
+  <si>
+    <t>PIP Gender-Responsive Just Energy Transition</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/01002479</t>
+  </si>
+  <si>
+    <t>Number of participants joining the focus group discussion on gender mainstreaming for just energy transition</t>
+  </si>
+  <si>
+    <t>40 participants</t>
+  </si>
+  <si>
+    <t>Achievement: total 45 participants joined and 37 participant are women</t>
+  </si>
+  <si>
+    <t>00106637</t>
+  </si>
+  <si>
+    <t>Partnership for Action on Green Economy</t>
+  </si>
+  <si>
+    <t>https://www.un-pageindonesia.org/
+https://open.undp.org/projects/00105341</t>
+  </si>
+  <si>
+    <t>The effective integration of Inclusive Green Economy (IGE) principles into Indonesia's national economic and development planning, evidenced by multi-stakeholder collaboration, sectoral and thematic reforms aligned with IGE priorities, and enhanced capacities at the individual, institutional, and planning levels for sustained IGE action</t>
+  </si>
+  <si>
+    <t>3 sectors
+4 document</t>
+  </si>
+  <si>
+    <t>From 2019 to 2024, PAGE Indonesia has provided support and interventions to facilitate Indonesia's green economy transition across three key sectors: energy, waste, and industry.
+PAGE Indonesia has produced and released over four key documents, including the Circular Economy Roadmap and Action Plan, support for the development of the Low Carbon Development Plan for West Java Province, the Regional Food Loss and Waste Strategy for Bali Province, a Green Recovery Assessment focusing on circular economy in the food and beverage industry, and an Electric Vehicle (EV) assessment linked to the Green Economy Index.</t>
+  </si>
+  <si>
+    <t>MPTF</t>
+  </si>
+  <si>
+    <t>Green and Circular Economy</t>
+  </si>
+  <si>
+    <t>National and Regional Level</t>
+  </si>
+  <si>
+    <t>00131053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sustainable Infrastructure Programme in Asia </t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00143365</t>
+  </si>
+  <si>
+    <t>The indicators include the number of feasibility studies on sustainable and low-carbon infrastructure projects used to mobilize investments, the number of stakeholders (disaggregated by gender) engaged through workshops on low-carbon and nature-positive strategies, and the inclusion of women in the design and implementation of these strategies, particularly in feasibility studies.</t>
+  </si>
+  <si>
+    <t>4 consultation workshop
+2 RDF Studies</t>
+  </si>
+  <si>
+    <t>As of November 2024, the SIPA project has conducted two consultation workshops, and one RDF roadmap assessment/study is currently in progress. The remaining workshops and studies are scheduled for 2025 rest of workshop and studies will be conducted in 2025</t>
+  </si>
+  <si>
+    <t>BMUV-IKI</t>
+  </si>
+  <si>
+    <t>Sustainable Infrastrcuture</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
     <t>Accel. Clean Energy Access to Reduce Inequality (ACCESS)</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00126434</t>
-  </si>
-  <si>
-    <t>Electricity Access</t>
   </si>
   <si>
     <r>
@@ -136,7 +619,12 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">3025 HH
+    <t xml:space="preserve">Baseline 2020
+‘0
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,025 HH
 </t>
   </si>
   <si>
@@ -144,98 +632,41 @@
 </t>
   </si>
   <si>
-    <t>KOICA</t>
-  </si>
-  <si>
-    <t>Non-VF</t>
-  </si>
-  <si>
-    <t>Close the gap on energy access</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>Capacity Building Training</t>
-  </si>
-  <si>
-    <t>Numbers of local people trained in field training on operation &amp; maintenance and passed post-test (disaggregated by gender).</t>
+    <t>Capacity Training</t>
+  </si>
+  <si>
+    <t>‘0</t>
   </si>
   <si>
     <t>achieved – 50 (46% women)</t>
   </si>
   <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t>Establishment of village electricity enterprise (BUMDES Listrik Desa) or Renewable Energy Service Cooperative (RESCO).</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> In seven villages in Indonesia target locations (pre-FS result)</t>
-  </si>
-  <si>
-    <t>Campaign Participant</t>
-  </si>
-  <si>
-    <t>Number of participants from stakeholder's institutions (government, private, donors, NGOs, regional development banks) receiving dissemination products, cumulative</t>
+    <t>‘Seven villages in Indonesia target locations (pre-FS result)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 </t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>663</t>
-  </si>
-  <si>
-    <t>PIP Accelerating Robust Carbon Pricing</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00142434</t>
   </si>
   <si>
     <t xml:space="preserve">#govt staffs certified as emission reduction verifiers;
 </t>
   </si>
   <si>
-    <t>JSB</t>
-  </si>
-  <si>
-    <t>Accelerating just energy transition</t>
+    <t>Energy Efficiency</t>
   </si>
   <si>
     <t>#mitigation actions registered in national registry system</t>
   </si>
   <si>
-    <t>Renewable Energy</t>
-  </si>
-  <si>
-    <t>NDC Support</t>
-  </si>
-  <si>
-    <t>Decarbonization</t>
-  </si>
-  <si>
-    <t>National</t>
-  </si>
-  <si>
-    <t>#people being involved in capacity building and policy dialogue</t>
-  </si>
-  <si>
-    <t>Electric Vehicles in Indonesia (ENTREV)</t>
-  </si>
-  <si>
     <t>PIMS+</t>
   </si>
   <si>
-    <t>Transportation and E-mobility Services</t>
-  </si>
-  <si>
-    <t>Number of direct project beneficiaries disaggregated by gender (individual people) [GEF core indicator]</t>
-  </si>
-  <si>
-    <t>GEF</t>
-  </si>
-  <si>
-    <t>VF</t>
-  </si>
-  <si>
-    <t>ADLIGHT</t>
+    <t>Other Energy Services</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -253,52 +684,7 @@
     <t>#6 manufacturers (1 for each association)</t>
   </si>
   <si>
-    <t>RE Market Transformation (NAMA)</t>
-  </si>
-  <si>
-    <t>Cumulative number of additional households (from baseline) having access to electricity in pilot provinces</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>320000 HH</t>
-  </si>
-  <si>
     <t>Achievement 327,667</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline 2020
-‘0
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,025 HH
-</t>
-  </si>
-  <si>
-    <t>Capacity Training</t>
-  </si>
-  <si>
-    <t>‘0</t>
-  </si>
-  <si>
-    <t>‘Seven villages in Indonesia target locations (pre-FS result)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 </t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Energy Efficiency</t>
-  </si>
-  <si>
-    <t>Other Energy Services</t>
   </si>
   <si>
     <t>Commensts</t>
@@ -346,9 +732,6 @@
     <t>350 people involved</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -371,9 +754,6 @@
     <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.) </t>
   </si>
   <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
     <t>Number of MW installed capacity</t>
   </si>
   <si>
@@ -416,33 +796,21 @@
     <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
   </si>
   <si>
-    <t>Energy Efficiency Services</t>
-  </si>
-  <si>
     <t xml:space="preserve">Number of MJ saved from energy efficiency interventions (e.g., building efficiency, industries, etc.)  </t>
   </si>
   <si>
-    <t>Energy Infrastructure Services</t>
-  </si>
-  <si>
     <t>Number of people who benefits from energy infrastructure interventions (streetlight, transmission, and distribution lines, etc.) </t>
   </si>
   <si>
     <t>Access to other service (electric vehicles, industries efficiency etc.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Financing support </t>
-  </si>
-  <si>
     <t xml:space="preserve">Support for the development of market ecosystem </t>
   </si>
   <si>
     <t>Support for the development of medium enterprises in the energy transition market</t>
   </si>
   <si>
-    <t>Small Enterprises</t>
-  </si>
-  <si>
     <t>Support for the development of small enterprises in the energy transition market</t>
   </si>
   <si>
@@ -453,9 +821,6 @@
   </si>
   <si>
     <t>Training for enterprises on the energy business is assumed to result in at least 100 direct beneficiaries</t>
-  </si>
-  <si>
-    <t>Market Intervention</t>
   </si>
   <si>
     <t xml:space="preserve">Volume of investment (US dollars) leverage removing barriers to private and public investment in clean, reliable, affordable, and sustainable energy solutions and energy efficiency for social infrastructure, productive use of electricity and other services </t>
@@ -474,7 +839,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <numFmts count="1">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+  </numFmts>
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,6 +919,28 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -566,7 +956,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -627,35 +1017,54 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -673,25 +1082,46 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -723,99 +1153,250 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -835,13 +1416,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -869,6 +1450,16 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Dzul Afifah Arifin" id="{04264E1D-CB01-4A26-8027-80662AEF9834}" userId="dzul.arifin@undp.org" providerId="PeoplePicker"/>
+  <person displayName="Heri Tabadepu" id="{9D88A0A3-9F7D-47D5-9EE7-46AA50DAF00C}" userId="heri.tabadepu@undp.org" providerId="PeoplePicker"/>
+  <person displayName="Mathilde Sari Gokmauli" id="{A8388F1E-DCBC-4722-A233-40313B3AEA19}" userId="mathilde.gokmauli@undp.org" providerId="PeoplePicker"/>
+  <person displayName="Sugiyanto Sugiyanto" id="{F8747D21-6DB8-4458-BF78-7C9B31453FEE}" userId="sugiyanto.sugiyanto@undp.org" providerId="PeoplePicker"/>
+  <person displayName="Gwyneth Anne Palmos" id="{A74E45B1-127A-4C91-91F4-02B14EAA5C17}" userId="S::gwyneth.anne.palmos@undp.org::4598e08f-a9dc-48c7-8201-9add67cb183b" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1156,23 +1747,57 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B2" dT="2024-11-21T01:49:17.20" personId="{A74E45B1-127A-4C91-91F4-02B14EAA5C17}" id="{8D1850B6-7295-40DA-83A4-1A6D64245AA8}">
+    <text>@Mathilde Sari Gokmauli @Sugiyanto Sugiyanto Please update data for ACCESS. Feel free to include relevant indicators that have not been reflected here</text>
+    <mentions>
+      <mention mentionpersonId="{A8388F1E-DCBC-4722-A233-40313B3AEA19}" mentionId="{026E60F7-5635-4E7D-828B-58AA6519287B}" startIndex="0" length="23"/>
+      <mention mentionpersonId="{F8747D21-6DB8-4458-BF78-7C9B31453FEE}" mentionId="{D3F70FF6-EBA6-49BD-89DD-92CF2E8721BC}" startIndex="24" length="20"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="B12" dT="2024-11-21T01:51:52.57" personId="{A74E45B1-127A-4C91-91F4-02B14EAA5C17}" id="{8CCC4E43-5BC1-43AE-8F36-8B20E99C45BE}">
+    <text>@Heri Tabadepu @Dzul Afifah Arifin Can you update the information here for the Carbon Pricing Project? Feel free to add relevant indicators not captured here</text>
+    <mentions>
+      <mention mentionpersonId="{9D88A0A3-9F7D-47D5-9EE7-46AA50DAF00C}" mentionId="{8CA6F148-B60B-4EF3-8175-CE52B20B3D9E}" startIndex="0" length="14"/>
+      <mention mentionpersonId="{04264E1D-CB01-4A26-8027-80662AEF9834}" mentionId="{A32A6949-7B15-42A6-AD81-BE662C64A48D}" startIndex="15" length="19"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="B26" dT="2024-11-21T01:53:02.06" personId="{A74E45B1-127A-4C91-91F4-02B14EAA5C17}" id="{74C36888-33F0-4E51-8559-FC66D10B7C5A}">
+    <text>@Heri Tabadepu Can you review details for MTRE3 and add/update as necessary?</text>
+    <mentions>
+      <mention mentionpersonId="{9D88A0A3-9F7D-47D5-9EE7-46AA50DAF00C}" mentionId="{9D2DE073-363F-45CE-9EB8-808C06CE8BC5}" startIndex="0" length="14"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="B33" dT="2024-11-21T02:03:01.47" personId="{A74E45B1-127A-4C91-91F4-02B14EAA5C17}" id="{E195C2DF-08F3-4FAE-AE76-17FBF46E5A37}">
+    <text xml:space="preserve">@Heri Tabadepu @Dzul Afifah Arifin Can you help populate data for this project? </text>
+    <mentions>
+      <mention mentionpersonId="{9D88A0A3-9F7D-47D5-9EE7-46AA50DAF00C}" mentionId="{3AC7304B-C24D-4551-B9A1-A2EEBCCB200B}" startIndex="0" length="14"/>
+      <mention mentionpersonId="{04264E1D-CB01-4A26-8027-80662AEF9834}" mentionId="{DCEFBA92-CF3D-4DB2-9C9B-13CAB9FC2EE7}" startIndex="15" length="19"/>
+    </mentions>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{518C8F51-08F6-47E6-92E7-B434FA427851}">
-  <dimension ref="A1:U15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{518C8F51-08F6-47E6-92E7-B434FA427851}">
+  <dimension ref="A1:U44"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="3"/>
-    <col min="2" max="3" width="20.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="3"/>
+    <col min="1" max="1" width="10.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="40" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="59" customWidth="1"/>
+    <col min="4" max="4" width="13" style="59" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="64.7109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.7109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="32.7109375" style="3" customWidth="1"/>
-    <col min="10" max="11" width="9.140625" style="3"/>
+    <col min="7" max="7" width="8.5703125" style="75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.7109375" style="76" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" style="75" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="3"/>
+    <col min="11" max="11" width="9.140625" style="48"/>
     <col min="12" max="12" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.140625" style="3"/>
-    <col min="14" max="14" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.28515625" style="3" customWidth="1"/>
     <col min="15" max="15" width="17.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.140625" style="3"/>
     <col min="17" max="17" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
@@ -1184,571 +1809,1632 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="45.75">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="38" t="s">
+      <c r="L1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="M1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="N1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="39" t="s">
+      <c r="P1" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="39" t="s">
+      <c r="Q1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="40" t="s">
+      <c r="R1" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="40" t="s">
+      <c r="T1" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="41" t="s">
+      <c r="U1" s="26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="72.75" customHeight="1">
-      <c r="A2" s="16">
+    <row r="2" spans="1:21" ht="60.75">
+      <c r="A2" s="81">
         <v>126434</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="78">
         <v>15028509</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="21">
+      <c r="G2" s="15">
         <v>0</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="21"/>
-      <c r="L2" s="42" t="s">
+      <c r="K2" s="41"/>
+      <c r="L2" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="35"/>
-      <c r="N2" s="43" t="s">
+      <c r="M2" s="17"/>
+      <c r="N2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="44" t="s">
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="35"/>
-      <c r="U2" s="44"/>
-    </row>
-    <row r="3" spans="1:21" ht="45.75">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="19" t="s">
+      <c r="T2" s="17"/>
+      <c r="U2" s="19"/>
+    </row>
+    <row r="3" spans="1:21" ht="30.75">
+      <c r="A3" s="82"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="G3" s="15">
+        <v>0</v>
+      </c>
+      <c r="H3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="21">
+      <c r="I3" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="18"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="19"/>
+    </row>
+    <row r="4" spans="1:21" ht="30.75">
+      <c r="A4" s="82"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="15">
         <v>0</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H4" s="41">
         <v>50</v>
       </c>
-      <c r="I3" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="22"/>
-      <c r="K3" s="27">
+      <c r="I4" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="18"/>
+      <c r="K4" s="71">
+        <v>0.42</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="17"/>
+      <c r="N4" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="19"/>
+    </row>
+    <row r="5" spans="1:21" ht="30.75">
+      <c r="A5" s="82"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0</v>
+      </c>
+      <c r="H5" s="42">
+        <v>21</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="18"/>
+      <c r="K5" s="71">
+        <v>0.46</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="19"/>
+    </row>
+    <row r="6" spans="1:21" ht="45.75">
+      <c r="A6" s="82"/>
+      <c r="B6" s="85"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="42">
+        <v>600</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="18"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="17"/>
+      <c r="N6" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="19"/>
+    </row>
+    <row r="7" spans="1:21" ht="30.75">
+      <c r="A7" s="82"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0</v>
+      </c>
+      <c r="H7" s="42">
+        <v>22</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="18"/>
+      <c r="K7" s="71">
+        <v>1.36</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="17"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="19"/>
+    </row>
+    <row r="8" spans="1:21" ht="30.75">
+      <c r="A8" s="82"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="18"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="17"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="19"/>
+    </row>
+    <row r="9" spans="1:21" ht="30.75">
+      <c r="A9" s="82"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0</v>
+      </c>
+      <c r="H9" s="42">
+        <v>22</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="18"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="19"/>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="83"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="16"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="19"/>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="63"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="19"/>
+    </row>
+    <row r="12" spans="1:21" ht="32.25" customHeight="1">
+      <c r="A12" s="81">
+        <v>142434</v>
+      </c>
+      <c r="B12" s="84" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="78">
+        <v>1796132</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0</v>
+      </c>
+      <c r="H12" s="41">
+        <v>10</v>
+      </c>
+      <c r="I12" s="15"/>
+      <c r="J12" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="17"/>
+      <c r="N12" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="19"/>
+    </row>
+    <row r="13" spans="1:21" ht="30.75">
+      <c r="A13" s="82"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0</v>
+      </c>
+      <c r="H13" s="42">
+        <v>329</v>
+      </c>
+      <c r="I13" s="15"/>
+      <c r="J13" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="41"/>
+      <c r="L13" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="17"/>
+      <c r="N13" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="O13" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="R13" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="S13" s="19"/>
+      <c r="T13" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="U13" s="19"/>
+    </row>
+    <row r="14" spans="1:21" ht="30.75">
+      <c r="A14" s="83"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0</v>
+      </c>
+      <c r="H14" s="42">
+        <v>350</v>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" s="17"/>
+      <c r="N14" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="19"/>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" s="64"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="19"/>
+    </row>
+    <row r="16" spans="1:21" ht="45.75">
+      <c r="A16" s="15">
+        <v>6333</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="56">
+        <v>1816500</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="15">
+        <v>0</v>
+      </c>
+      <c r="H16" s="43">
+        <v>643224</v>
+      </c>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" s="71">
+        <v>0.24</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" s="17"/>
+      <c r="N16" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="19"/>
+    </row>
+    <row r="17" spans="1:21" ht="30.75">
+      <c r="A17" s="15"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="15">
+        <v>0</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="19"/>
+    </row>
+    <row r="18" spans="1:21" ht="45.75">
+      <c r="A18" s="15"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="15">
+        <v>0</v>
+      </c>
+      <c r="H18" s="44">
+        <v>241000</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J18" s="15"/>
+      <c r="K18" s="71">
         <v>0.3</v>
       </c>
-      <c r="L3" s="42" t="s">
+      <c r="L18" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" s="17"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="19"/>
+    </row>
+    <row r="19" spans="1:21" ht="259.5">
+      <c r="A19" s="15"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="15">
+        <v>0</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M19" s="17"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="19"/>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" s="15"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="19"/>
+    </row>
+    <row r="21" spans="1:21" ht="30.75">
+      <c r="A21" s="81">
+        <v>5721</v>
+      </c>
+      <c r="B21" s="84" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="93" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="78">
+        <v>2633372</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="15">
+        <v>0</v>
+      </c>
+      <c r="H21" s="41">
+        <v>6</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M21" s="17"/>
+      <c r="N21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="19"/>
+    </row>
+    <row r="22" spans="1:21" ht="45.75">
+      <c r="A22" s="82"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="94"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="15">
+        <v>0</v>
+      </c>
+      <c r="H22" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="J22" s="22"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M22" s="17"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="19"/>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="82"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="15">
+        <v>0</v>
+      </c>
+      <c r="H23" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="K23" s="41"/>
+      <c r="L23" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M23" s="17"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="19"/>
+    </row>
+    <row r="24" spans="1:21" ht="30.75">
+      <c r="A24" s="83"/>
+      <c r="B24" s="86"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" s="15">
+        <v>0</v>
+      </c>
+      <c r="H24" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J24" s="22"/>
+      <c r="K24" s="71">
+        <v>0.4</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M24" s="17"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="19"/>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="63"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="19"/>
+    </row>
+    <row r="26" spans="1:21" ht="30.75">
+      <c r="A26" s="81">
+        <v>4673</v>
+      </c>
+      <c r="B26" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="93" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="78">
+        <v>8025000</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M26" s="17"/>
+      <c r="N26" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="19"/>
+    </row>
+    <row r="27" spans="1:21" ht="30.75">
+      <c r="A27" s="82"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G27" s="15">
+        <v>0</v>
+      </c>
+      <c r="H27" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="J27" s="15"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="19"/>
+    </row>
+    <row r="28" spans="1:21" ht="30.75">
+      <c r="A28" s="82"/>
+      <c r="B28" s="85"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" s="15">
+        <v>0</v>
+      </c>
+      <c r="H28" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="J28" s="15"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="19"/>
+    </row>
+    <row r="29" spans="1:21" ht="30.75">
+      <c r="A29" s="82"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="15">
+        <v>0</v>
+      </c>
+      <c r="H29" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="J29" s="37"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="19"/>
+    </row>
+    <row r="30" spans="1:21" ht="30.75">
+      <c r="A30" s="82"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" s="49">
+        <v>0</v>
+      </c>
+      <c r="H30" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="I30" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="J30" s="36"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="19"/>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" s="83"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G31" s="15">
+        <v>0</v>
+      </c>
+      <c r="H31" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="I31" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="J31" s="54"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="19"/>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" s="64"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="51"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="74"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="19"/>
+    </row>
+    <row r="33" spans="1:21" s="35" customFormat="1" ht="76.5">
+      <c r="A33" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" s="60">
+        <v>1976199</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33" s="15">
+        <v>0</v>
+      </c>
+      <c r="H33" s="41"/>
+      <c r="I33" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="J33" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="K33" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="35"/>
-      <c r="N3" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="44"/>
-    </row>
-    <row r="4" spans="1:21" ht="45.75">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="21">
+      <c r="M33" s="32"/>
+      <c r="N33" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="O33" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="R33" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="S33" s="34"/>
+      <c r="T33" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="U33" s="34"/>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" s="15"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="19"/>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" s="15"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="19"/>
+    </row>
+    <row r="36" spans="1:21" ht="45.75">
+      <c r="A36" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="56">
+        <v>150000</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="15">
         <v>0</v>
       </c>
-      <c r="H4" s="26">
-        <v>21</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="22"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="42" t="s">
+      <c r="H36" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="J36" s="20"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="35"/>
-      <c r="N4" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="44"/>
-    </row>
-    <row r="5" spans="1:21" ht="45.75">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="20"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="20"/>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" s="21"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="47"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="20"/>
+      <c r="T37" s="20"/>
+      <c r="U37" s="20"/>
+    </row>
+    <row r="38" spans="1:21" s="75" customFormat="1" ht="45.75">
+      <c r="A38" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="56">
+        <v>150000</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" s="15">
         <v>0</v>
       </c>
-      <c r="H5" s="26">
-        <v>600</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="42" t="s">
+      <c r="H38" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="J38" s="15"/>
+      <c r="K38" s="71">
+        <v>0.75</v>
+      </c>
+      <c r="L38" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="M5" s="35"/>
-      <c r="N5" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="44"/>
-    </row>
-    <row r="6" spans="1:21" ht="45.75">
-      <c r="A6" s="16">
-        <v>142434</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="18">
-        <v>1796132</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="26">
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="15"/>
+    </row>
+    <row r="39" spans="1:21">
+      <c r="A39" s="20"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="47"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+    </row>
+    <row r="40" spans="1:21" ht="321">
+      <c r="A40" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" s="56">
+        <v>1116810.3600000001</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G40" s="15">
         <v>0</v>
       </c>
-      <c r="H6" s="21">
-        <v>10</v>
-      </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="21"/>
-      <c r="L6" s="42" t="s">
+      <c r="H40" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="K40" s="47"/>
+      <c r="L40" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="35"/>
-      <c r="N6" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="44"/>
-    </row>
-    <row r="7" spans="1:21" ht="45.75">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="19" t="s">
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="20"/>
+      <c r="T40" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="U40" s="20"/>
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41" s="20"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="47"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="20"/>
+    </row>
+    <row r="42" spans="1:21" ht="137.25">
+      <c r="A42" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" s="56">
+        <v>315717.74</v>
+      </c>
+      <c r="E42" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="26">
+      <c r="F42" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="G42" s="15">
         <v>0</v>
       </c>
-      <c r="H7" s="26">
-        <v>329</v>
-      </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="42" t="s">
+      <c r="H42" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="K42" s="47"/>
+      <c r="L42" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="35"/>
-      <c r="N7" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="O7" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="R7" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="S7" s="44"/>
-      <c r="T7" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="U7" s="44"/>
-    </row>
-    <row r="8" spans="1:21" ht="45.75">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="26">
-        <v>0</v>
-      </c>
-      <c r="H8" s="26">
-        <v>350</v>
-      </c>
-      <c r="I8" s="21"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="35"/>
-      <c r="N8" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="44"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="44"/>
-    </row>
-    <row r="9" spans="1:21" ht="45.75">
-      <c r="A9" s="31">
-        <v>6333</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="31">
-        <v>1816500</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="21">
-        <v>0</v>
-      </c>
-      <c r="H9" s="32">
-        <v>643224</v>
-      </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="K9" s="27">
-        <v>0.24</v>
-      </c>
-      <c r="L9" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="M9" s="35"/>
-      <c r="N9" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="44"/>
-    </row>
-    <row r="10" spans="1:21" ht="91.5">
-      <c r="A10" s="16">
-        <v>5721</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="18">
-        <v>2633372</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="21">
-        <v>125</v>
-      </c>
-      <c r="I10" s="21"/>
-      <c r="J10" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10" s="27">
-        <v>0.34</v>
-      </c>
-      <c r="L10" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="M10" s="35"/>
-      <c r="N10" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="44"/>
-    </row>
-    <row r="11" spans="1:21" ht="45.75">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="33">
-        <v>6</v>
-      </c>
-      <c r="H11" s="21">
-        <v>10</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="J11" s="18"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="M11" s="35"/>
-      <c r="N11" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="44"/>
-    </row>
-    <row r="12" spans="1:21" ht="45.75">
-      <c r="A12" s="34">
-        <v>4673</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="34">
-        <v>8025000</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="26" t="s">
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="20"/>
+      <c r="T42" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="21"/>
-      <c r="L12" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="35"/>
-      <c r="N12" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="44"/>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="6"/>
+      <c r="U42" s="20"/>
+    </row>
+    <row r="43" spans="1:21">
+      <c r="A43" s="20"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="47"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
+    </row>
+    <row r="44" spans="1:21">
+      <c r="A44" s="20"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="47"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="20"/>
+      <c r="T44" s="20"/>
+      <c r="U44" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D2:D10"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="D26:D31"/>
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="B2:B10"/>
+    <mergeCell ref="C2:C10"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="C26:C31"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A26:A31"/>
+  </mergeCells>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q12" xr:uid="{89DF9B0E-F0F9-4D3A-8ED3-C868504BD11F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q35" xr:uid="{89DF9B0E-F0F9-4D3A-8ED3-C868504BD11F}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P12" xr:uid="{A0C998CC-C8EA-4ABE-AF8D-086FF386049A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P35" xr:uid="{A0C998CC-C8EA-4ABE-AF8D-086FF386049A}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N12" xr:uid="{009BAAA6-FB2F-484B-9AF3-58B52DDDC00B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N35" xr:uid="{009BAAA6-FB2F-484B-9AF3-58B52DDDC00B}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O12" xr:uid="{93C2954B-8D6F-4B41-BB64-7A7FB8F2C484}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O35" xr:uid="{93C2954B-8D6F-4B41-BB64-7A7FB8F2C484}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L12" xr:uid="{C5D05071-5D90-4A13-9D21-B9EBD6EE39FE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L35" xr:uid="{C5D05071-5D90-4A13-9D21-B9EBD6EE39FE}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M12" xr:uid="{6E7EBC8A-ABDB-42A7-8B65-4EA10A315E1D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M35" xr:uid="{6E7EBC8A-ABDB-42A7-8B65-4EA10A315E1D}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T12" xr:uid="{AEC6DEB2-D5E4-4B9F-84FF-21A7F99E858B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T35" xr:uid="{AEC6DEB2-D5E4-4B9F-84FF-21A7F99E858B}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R12" xr:uid="{98C3269F-4DF8-4538-9154-9C48016DCDAB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R35" xr:uid="{98C3269F-4DF8-4538-9154-9C48016DCDAB}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S12" xr:uid="{72A5E88B-D3D9-470C-A53D-3E9B1EB09100}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S35" xr:uid="{72A5E88B-D3D9-470C-A53D-3E9B1EB09100}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{2981B45F-4B0D-405F-91A6-63012678890F}"/>
-    <hyperlink ref="C6" r:id="rId2" xr:uid="{363864F6-7D4B-4287-AD36-C2FC6197422D}"/>
+    <hyperlink ref="C12" r:id="rId2" xr:uid="{363864F6-7D4B-4287-AD36-C2FC6197422D}"/>
+    <hyperlink ref="C26" r:id="rId3" xr:uid="{82091ED5-F29D-4345-951E-27BD04C8FB37}"/>
+    <hyperlink ref="C21" r:id="rId4" xr:uid="{58A876F6-0A1B-4D17-B147-E67138EDB542}"/>
+    <hyperlink ref="C16" r:id="rId5" xr:uid="{422DE5E3-15B2-4E27-BB4C-79128A74AC27}"/>
+    <hyperlink ref="C33" r:id="rId6" xr:uid="{FEA99C7D-737E-4A0C-A4EB-88F4D6968550}"/>
+    <hyperlink ref="C38" r:id="rId7" xr:uid="{B3B46140-41E7-4E9B-A7FB-007F4393E638}"/>
+    <hyperlink ref="C36" r:id="rId8" xr:uid="{74C55B10-8228-4F1D-AB93-D6A186BDEF49}"/>
+    <hyperlink ref="C40" r:id="rId9" display="https://www.un-pageindonesia.org/" xr:uid="{3A866736-0ADA-41D9-939C-BCDB6FC6E558}"/>
+    <hyperlink ref="C42" r:id="rId10" xr:uid="{D135F87E-3545-491F-9567-80534C335A53}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId11"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -1756,13 +3442,13 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E13:E22</xm:sqref>
+          <xm:sqref>E45</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5EC3B4A4-95B1-4F78-9238-587D34E121D0}">
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E12</xm:sqref>
+          <xm:sqref>E2:E44</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1773,7 +3459,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F287A9AF-FA29-4E61-82D7-058611A28862}">
   <dimension ref="A1:T15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
     <col min="2" max="3" width="20.7109375" style="3" customWidth="1"/>
@@ -1785,7 +3471,7 @@
     <col min="10" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30.75">
+    <row r="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1820,7 +3506,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="M1" s="10"/>
       <c r="N1" s="10"/>
@@ -1842,67 +3528,67 @@
       <c r="T1" s="10"/>
     </row>
     <row r="2" spans="1:20" ht="72.75" customHeight="1">
-      <c r="A2" s="45">
+      <c r="A2" s="96">
         <v>126434</v>
       </c>
-      <c r="B2" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="51" t="s">
+      <c r="B2" s="96" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="45">
+      <c r="D2" s="96">
         <v>15028509</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="J2" s="98" t="s">
         <v>27</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="60.75">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="50"/>
+    <row r="3" spans="1:20" ht="57.95">
+      <c r="A3" s="101"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="101"/>
       <c r="E3" s="1" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="H3" s="1">
         <v>50</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="48"/>
+        <v>161</v>
+      </c>
+      <c r="J3" s="99"/>
       <c r="K3" s="11">
         <v>0.3</v>
       </c>
@@ -1910,195 +3596,195 @@
         <v>28</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="60.75">
-      <c r="A4" s="50"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="50"/>
+    <row r="4" spans="1:20" ht="57.95">
+      <c r="A4" s="101"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="101"/>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="H4" s="5">
         <v>21</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" s="48"/>
+        <v>163</v>
+      </c>
+      <c r="J4" s="99"/>
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="60.75">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="46"/>
+    <row r="5" spans="1:20" ht="57.95">
+      <c r="A5" s="97"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="97"/>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="H5" s="5">
         <v>600</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="49"/>
+        <v>165</v>
+      </c>
+      <c r="J5" s="100"/>
       <c r="L5" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="60.75">
-      <c r="A6" s="45">
+    <row r="6" spans="1:20" ht="57.95">
+      <c r="A6" s="96">
         <v>142434</v>
       </c>
-      <c r="B6" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="45">
+      <c r="B6" s="96" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="102" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="96">
         <v>1796132</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="H6" s="1">
         <v>10</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="45" t="s">
-        <v>43</v>
+      <c r="J6" s="96" t="s">
+        <v>58</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="60.75">
-      <c r="A7" s="50"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="50"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="57.95">
+      <c r="A7" s="101"/>
+      <c r="B7" s="101"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="101"/>
       <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="H7" s="5">
         <v>329</v>
       </c>
       <c r="I7" s="1"/>
-      <c r="J7" s="50"/>
+      <c r="J7" s="101"/>
       <c r="L7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="60.75">
-      <c r="A8" s="46"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="46"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="57.95">
+      <c r="A8" s="97"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="97"/>
       <c r="E8" s="1" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="H8" s="5">
         <v>350</v>
       </c>
       <c r="I8" s="1"/>
-      <c r="J8" s="46"/>
+      <c r="J8" s="97"/>
       <c r="L8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="60.75">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="57.95">
       <c r="A9" s="4">
         <v>6333</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="D9" s="4">
         <v>1816500</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>76</v>
+        <v>170</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="12">
@@ -2106,101 +3792,101 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="K9" s="11">
         <v>0.24</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="91.5">
-      <c r="A10" s="45">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="87">
+      <c r="A10" s="96">
         <v>5721</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="45">
+      <c r="B10" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="96" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="96">
         <v>2633372</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>59</v>
+        <v>172</v>
       </c>
       <c r="H10" s="1">
         <v>125</v>
       </c>
       <c r="I10" s="1"/>
-      <c r="J10" s="45" t="s">
-        <v>55</v>
+      <c r="J10" s="96" t="s">
+        <v>70</v>
       </c>
       <c r="K10" s="11">
         <v>0.34</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="60.75">
-      <c r="A11" s="46"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="57.95">
+      <c r="A11" s="97"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
       </c>
       <c r="I11" s="1"/>
-      <c r="J11" s="46"/>
+      <c r="J11" s="97"/>
       <c r="L11" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="60.75">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="57.95">
       <c r="A12" s="4">
         <v>4673</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="D12" s="4">
         <v>8025000</v>
@@ -2209,25 +3895,25 @@
         <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>23</v>
@@ -2294,7 +3980,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
     <col min="2" max="3" width="20.7109375" style="3" customWidth="1"/>
@@ -2307,7 +3993,7 @@
     <col min="12" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30.75">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2339,290 +4025,290 @@
         <v>8</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="72.75" customHeight="1">
-      <c r="A2" s="45">
+      <c r="A2" s="96">
         <v>126434</v>
       </c>
-      <c r="B2" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="51" t="s">
+      <c r="B2" s="96" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="45">
+      <c r="D2" s="96">
         <v>15028509</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="98" t="s">
         <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>26</v>
+        <v>158</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="30.75">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="48"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="29.1">
+      <c r="A3" s="101"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="99"/>
       <c r="F3" s="1" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30.75">
-      <c r="A4" s="50"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="48"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="29.1">
+      <c r="A4" s="101"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="99"/>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="45.75">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="49"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="43.5">
+      <c r="A5" s="97"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="100"/>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="45.75">
-      <c r="A6" s="45">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="43.5">
+      <c r="A6" s="96">
         <v>142434</v>
       </c>
-      <c r="B6" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="45">
+      <c r="B6" s="96" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="102" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="96">
         <v>1796132</v>
       </c>
-      <c r="E6" s="45" t="s">
-        <v>43</v>
+      <c r="E6" s="96" t="s">
+        <v>58</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="50"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
+      <c r="A7" s="101"/>
+      <c r="B7" s="101"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="101"/>
       <c r="F7" s="1" t="s">
-        <v>76</v>
+        <v>170</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="46"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
+      <c r="A8" s="97"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
       <c r="F8" s="1" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="121.5">
+    <row r="9" spans="1:11" ht="116.1">
       <c r="A9" s="4">
         <v>6333</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="D9" s="4">
         <v>1816500</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>87</v>
+        <v>185</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>88</v>
+        <v>186</v>
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:11" ht="91.5">
-      <c r="A10" s="45">
+    <row r="10" spans="1:11" ht="87">
+      <c r="A10" s="96">
         <v>5721</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="45">
+      <c r="B10" s="96" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="96" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="96">
         <v>2633372</v>
       </c>
-      <c r="E10" s="45" t="s">
-        <v>55</v>
+      <c r="E10" s="96" t="s">
+        <v>70</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>59</v>
+        <v>172</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="45.75">
-      <c r="A11" s="46"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
+    <row r="11" spans="1:11" ht="29.1">
+      <c r="A11" s="97"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
       <c r="F11" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:11" ht="45.75">
+    <row r="12" spans="1:11" ht="43.5">
       <c r="A12" s="4">
         <v>4673</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="D12" s="4">
         <v>8025000</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>91</v>
+        <v>189</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2669,185 +4355,185 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="2" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="54" t="s">
+    <row r="2" spans="1:2" ht="43.5">
+      <c r="A2" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>92</v>
+      <c r="B2" s="14" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="54" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="54" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="37" t="s">
+      <c r="A3" s="105" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="29.1">
+      <c r="A4" s="105" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="29.1">
+      <c r="A5" s="105" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="87">
+      <c r="A6" s="105" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="43.5">
+      <c r="A7" s="105" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="43.5">
+      <c r="A8" s="105" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="43.5">
+      <c r="A9" s="105" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="29.1">
+      <c r="A10" s="105" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="106" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="29.1">
+      <c r="A11" s="105" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="106" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="43.5">
+      <c r="A12" s="105" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="29.1">
+      <c r="A13" s="105" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="106" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="105" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="106" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="29.1">
+      <c r="A15" s="105" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="106" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="29.1">
+      <c r="A16" s="105" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="106" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="29.1">
+      <c r="A17" s="105" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29.1">
+      <c r="A18" s="105" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="106" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="72.599999999999994">
+      <c r="A19" s="105" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="54" t="s">
+      <c r="B19" s="106" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="29.1">
+      <c r="A20" s="105" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="106" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="43.5">
+      <c r="A21" s="105" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="107" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="29.1">
+      <c r="A22" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="55" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="B11" s="55" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="54" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="54" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" s="55" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="55" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="55" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="54" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" s="55" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="37" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="54" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18" s="55" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="54" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="55" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="55" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="56" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="55" t="s">
-        <v>125</v>
+      <c r="B22" s="106" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2856,6 +4542,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -2888,9 +4583,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2915,6 +4610,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2994,6 +4690,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3137,23 +4838,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2D7830B-D252-4AE4-BDBD-976B65B8A87C}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2031F88-137D-4398-9974-44E9D22D0D48}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FFF72CD-5C74-4F08-B7A2-C0DAE8F4E46E}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2D7830B-D252-4AE4-BDBD-976B65B8A87C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E04AC16-9AB0-44B4-AB84-2B0CEAD14365}"/>
 </file>
--- a/01_Input/00_CO Validation/Indonesia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Indonesia - Energy Projects.xlsx
@@ -324,7 +324,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -643,13 +643,11 @@
     <xf numFmtId="41" fontId="0" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -753,6 +751,8 @@
   <authors>
     <author>tc={8D1850B6-7295-40DA-83A4-1A6D64245AA8}</author>
     <author>tc={8CCC4E43-5BC1-43AE-8F36-8B20E99C45BE}</author>
+    <author>CO validation update</author>
+    <author>tc={74C36888-33F0-4E51-8559-FC66D10B7C5A}</author>
     <author>tc={E195C2DF-08F3-4FAE-AE76-17FBF46E5A37}</author>
   </authors>
   <commentList>
@@ -772,7 +772,35 @@
     @Heri Tabadepu @Dzul Afifah Arifin Can you update the information here for the Carbon Pricing Project? Feel free to add relevant indicators not captured here</t>
       </text>
     </comment>
-    <comment ref="B35" authorId="2" shapeId="0">
+    <comment ref="K20" authorId="2" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L20" authorId="2" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K26" authorId="2" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L26" authorId="2" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="3" shapeId="0">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    @Heri Tabadepu Can you review details for MTRE3 and add/update as necessary?</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="4" shapeId="0">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1298,14 +1326,6 @@
       <c r="X2" s="19" t="n"/>
     </row>
     <row r="3" ht="30.75" customHeight="1">
-      <c r="A3" s="110" t="n"/>
-      <c r="B3" s="110" t="n"/>
-      <c r="C3" s="110" t="n"/>
-      <c r="D3" s="110" t="n"/>
-      <c r="E3" s="110" t="n"/>
-      <c r="F3" s="110" t="n"/>
-      <c r="G3" s="110" t="n"/>
-      <c r="H3" s="110" t="n"/>
       <c r="I3" s="15" t="inlineStr">
         <is>
           <t>Electricity Access</t>
@@ -1342,14 +1362,6 @@
       <c r="X3" s="19" t="n"/>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="110" t="n"/>
-      <c r="B4" s="110" t="n"/>
-      <c r="C4" s="110" t="n"/>
-      <c r="D4" s="110" t="n"/>
-      <c r="E4" s="110" t="n"/>
-      <c r="F4" s="110" t="n"/>
-      <c r="G4" s="110" t="n"/>
-      <c r="H4" s="110" t="n"/>
       <c r="I4" s="15" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
@@ -1390,14 +1402,6 @@
       <c r="X4" s="19" t="n"/>
     </row>
     <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="110" t="n"/>
-      <c r="B5" s="110" t="n"/>
-      <c r="C5" s="110" t="n"/>
-      <c r="D5" s="110" t="n"/>
-      <c r="E5" s="110" t="n"/>
-      <c r="F5" s="110" t="n"/>
-      <c r="G5" s="110" t="n"/>
-      <c r="H5" s="110" t="n"/>
       <c r="I5" s="15" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
@@ -1438,14 +1442,6 @@
       <c r="X5" s="19" t="n"/>
     </row>
     <row r="6" ht="45.75" customHeight="1">
-      <c r="A6" s="110" t="n"/>
-      <c r="B6" s="110" t="n"/>
-      <c r="C6" s="110" t="n"/>
-      <c r="D6" s="110" t="n"/>
-      <c r="E6" s="110" t="n"/>
-      <c r="F6" s="110" t="n"/>
-      <c r="G6" s="110" t="n"/>
-      <c r="H6" s="110" t="n"/>
       <c r="I6" s="15" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
@@ -1484,14 +1480,6 @@
       <c r="X6" s="19" t="n"/>
     </row>
     <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="110" t="n"/>
-      <c r="B7" s="110" t="n"/>
-      <c r="C7" s="110" t="n"/>
-      <c r="D7" s="110" t="n"/>
-      <c r="E7" s="110" t="n"/>
-      <c r="F7" s="110" t="n"/>
-      <c r="G7" s="110" t="n"/>
-      <c r="H7" s="110" t="n"/>
       <c r="I7" s="15" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
@@ -1528,14 +1516,6 @@
       <c r="X7" s="19" t="n"/>
     </row>
     <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="110" t="n"/>
-      <c r="B8" s="110" t="n"/>
-      <c r="C8" s="110" t="n"/>
-      <c r="D8" s="110" t="n"/>
-      <c r="E8" s="110" t="n"/>
-      <c r="F8" s="110" t="n"/>
-      <c r="G8" s="110" t="n"/>
-      <c r="H8" s="110" t="n"/>
       <c r="I8" s="15" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -1572,14 +1552,6 @@
       <c r="X8" s="19" t="n"/>
     </row>
     <row r="9" ht="30.75" customHeight="1">
-      <c r="A9" s="110" t="n"/>
-      <c r="B9" s="110" t="n"/>
-      <c r="C9" s="110" t="n"/>
-      <c r="D9" s="110" t="n"/>
-      <c r="E9" s="110" t="n"/>
-      <c r="F9" s="110" t="n"/>
-      <c r="G9" s="110" t="n"/>
-      <c r="H9" s="110" t="n"/>
       <c r="I9" s="15" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
@@ -1614,14 +1586,6 @@
       <c r="X9" s="19" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="111" t="n"/>
-      <c r="B10" s="111" t="n"/>
-      <c r="C10" s="111" t="n"/>
-      <c r="D10" s="111" t="n"/>
-      <c r="E10" s="111" t="n"/>
-      <c r="F10" s="111" t="n"/>
-      <c r="G10" s="111" t="n"/>
-      <c r="H10" s="111" t="n"/>
       <c r="I10" s="15" t="inlineStr">
         <is>
           <t>Other</t>
@@ -1736,14 +1700,6 @@
       <c r="X12" s="19" t="n"/>
     </row>
     <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="110" t="n"/>
-      <c r="B13" s="110" t="n"/>
-      <c r="C13" s="110" t="n"/>
-      <c r="D13" s="110" t="n"/>
-      <c r="E13" s="110" t="n"/>
-      <c r="F13" s="110" t="n"/>
-      <c r="G13" s="110" t="n"/>
-      <c r="H13" s="110" t="n"/>
       <c r="I13" s="15" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -1798,14 +1754,6 @@
       <c r="X13" s="19" t="n"/>
     </row>
     <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="111" t="n"/>
-      <c r="B14" s="111" t="n"/>
-      <c r="C14" s="111" t="n"/>
-      <c r="D14" s="111" t="n"/>
-      <c r="E14" s="111" t="n"/>
-      <c r="F14" s="111" t="n"/>
-      <c r="G14" s="111" t="n"/>
-      <c r="H14" s="111" t="n"/>
       <c r="I14" s="15" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
@@ -2091,15 +2039,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K20" s="15" t="n">
+      <c r="K20" s="110" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="112" t="n"/>
-      <c r="M20" s="113" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L20" s="111" t="n"/>
+      <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="71" t="n"/>
       <c r="P20" s="17" t="n"/>
@@ -2139,14 +2083,30 @@
       <c r="X21" s="19" t="n"/>
     </row>
     <row r="22" ht="45.75" customHeight="1">
-      <c r="A22" s="110" t="n"/>
-      <c r="B22" s="110" t="n"/>
-      <c r="C22" s="110" t="n"/>
-      <c r="D22" s="110" t="n"/>
+      <c r="A22" s="18" t="n">
+        <v>5721</v>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>ADLIGHT</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="inlineStr">
+        <is>
+          <t>https://co.pims.undp.org/project/view?id=5721</t>
+        </is>
+      </c>
+      <c r="D22" s="56" t="n">
+        <v>2633372</v>
+      </c>
       <c r="E22" s="109" t="n"/>
       <c r="F22" s="109" t="n"/>
       <c r="G22" s="109" t="n"/>
-      <c r="H22" s="56" t="n"/>
+      <c r="H22" s="56" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
@@ -2189,14 +2149,6 @@
       <c r="X22" s="19" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="110" t="n"/>
-      <c r="B23" s="110" t="n"/>
-      <c r="C23" s="110" t="n"/>
-      <c r="D23" s="110" t="n"/>
-      <c r="E23" s="110" t="n"/>
-      <c r="F23" s="110" t="n"/>
-      <c r="G23" s="110" t="n"/>
-      <c r="H23" s="110" t="n"/>
       <c r="I23" s="15" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
@@ -2233,14 +2185,6 @@
       <c r="X23" s="19" t="n"/>
     </row>
     <row r="24" ht="30.75" customHeight="1">
-      <c r="A24" s="111" t="n"/>
-      <c r="B24" s="111" t="n"/>
-      <c r="C24" s="111" t="n"/>
-      <c r="D24" s="111" t="n"/>
-      <c r="E24" s="110" t="n"/>
-      <c r="F24" s="110" t="n"/>
-      <c r="G24" s="110" t="n"/>
-      <c r="H24" s="110" t="n"/>
       <c r="I24" s="15" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2281,14 +2225,6 @@
       <c r="X24" s="19" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="111" t="n"/>
-      <c r="B25" s="111" t="n"/>
-      <c r="C25" s="111" t="n"/>
-      <c r="D25" s="111" t="n"/>
-      <c r="E25" s="111" t="n"/>
-      <c r="F25" s="111" t="n"/>
-      <c r="G25" s="111" t="n"/>
-      <c r="H25" s="111" t="n"/>
       <c r="I25" s="15" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
@@ -2327,14 +2263,6 @@
       <c r="X25" s="19" t="n"/>
     </row>
     <row r="26" ht="30.75" customHeight="1">
-      <c r="A26" s="111" t="n"/>
-      <c r="B26" s="111" t="n"/>
-      <c r="C26" s="111" t="n"/>
-      <c r="D26" s="111" t="n"/>
-      <c r="E26" s="111" t="n"/>
-      <c r="F26" s="111" t="n"/>
-      <c r="G26" s="111" t="n"/>
-      <c r="H26" s="111" t="n"/>
       <c r="I26" s="15" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -2345,15 +2273,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K26" s="15" t="n">
+      <c r="K26" s="110" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="114" t="n"/>
-      <c r="M26" s="113" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L26" s="112" t="n"/>
+      <c r="M26" s="15" t="n"/>
       <c r="N26" s="22" t="n"/>
       <c r="O26" s="71" t="n"/>
       <c r="P26" s="17" t="n"/>
@@ -2367,10 +2291,10 @@
       <c r="X26" s="19" t="n"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
-      <c r="A27" s="110" t="n"/>
-      <c r="B27" s="110" t="n"/>
-      <c r="C27" s="110" t="n"/>
-      <c r="D27" s="110" t="n"/>
+      <c r="A27" s="82" t="n"/>
+      <c r="B27" s="85" t="n"/>
+      <c r="C27" s="94" t="n"/>
+      <c r="D27" s="79" t="n"/>
       <c r="E27" s="79" t="n"/>
       <c r="F27" s="79" t="n"/>
       <c r="G27" s="79" t="n"/>
@@ -2393,14 +2317,30 @@
       <c r="X27" s="19" t="n"/>
     </row>
     <row r="28" ht="30.75" customHeight="1">
-      <c r="A28" s="110" t="n"/>
-      <c r="B28" s="110" t="n"/>
-      <c r="C28" s="110" t="n"/>
-      <c r="D28" s="110" t="n"/>
+      <c r="A28" s="18" t="n">
+        <v>4673</v>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>RE Market Transformation (NAMA)</t>
+        </is>
+      </c>
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t>https://co.pims.undp.org/project/view?id=4673</t>
+        </is>
+      </c>
+      <c r="D28" s="56" t="n">
+        <v>8025000</v>
+      </c>
       <c r="E28" s="109" t="n"/>
       <c r="F28" s="109" t="n"/>
       <c r="G28" s="109" t="n"/>
-      <c r="H28" s="56" t="n"/>
+      <c r="H28" s="56" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
           <t>Electricity Access</t>
@@ -2447,14 +2387,6 @@
       <c r="X28" s="19" t="n"/>
     </row>
     <row r="29" ht="30.75" customHeight="1">
-      <c r="A29" s="110" t="n"/>
-      <c r="B29" s="110" t="n"/>
-      <c r="C29" s="110" t="n"/>
-      <c r="D29" s="110" t="n"/>
-      <c r="E29" s="110" t="n"/>
-      <c r="F29" s="110" t="n"/>
-      <c r="G29" s="110" t="n"/>
-      <c r="H29" s="110" t="n"/>
       <c r="I29" s="15" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -2495,14 +2427,6 @@
       <c r="X29" s="19" t="n"/>
     </row>
     <row r="30" ht="30.75" customHeight="1">
-      <c r="A30" s="110" t="n"/>
-      <c r="B30" s="110" t="n"/>
-      <c r="C30" s="110" t="n"/>
-      <c r="D30" s="110" t="n"/>
-      <c r="E30" s="110" t="n"/>
-      <c r="F30" s="110" t="n"/>
-      <c r="G30" s="110" t="n"/>
-      <c r="H30" s="110" t="n"/>
       <c r="I30" s="15" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
@@ -2539,14 +2463,6 @@
       <c r="X30" s="19" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="111" t="n"/>
-      <c r="B31" s="111" t="n"/>
-      <c r="C31" s="111" t="n"/>
-      <c r="D31" s="111" t="n"/>
-      <c r="E31" s="110" t="n"/>
-      <c r="F31" s="110" t="n"/>
-      <c r="G31" s="110" t="n"/>
-      <c r="H31" s="110" t="n"/>
       <c r="I31" s="15" t="inlineStr">
         <is>
           <t>Market Intervention</t>
@@ -2587,14 +2503,6 @@
       <c r="X31" s="19" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="110" t="n"/>
-      <c r="B32" s="110" t="n"/>
-      <c r="C32" s="110" t="n"/>
-      <c r="D32" s="110" t="n"/>
-      <c r="E32" s="110" t="n"/>
-      <c r="F32" s="110" t="n"/>
-      <c r="G32" s="110" t="n"/>
-      <c r="H32" s="110" t="n"/>
       <c r="I32" s="15" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
@@ -2631,14 +2539,6 @@
       <c r="X32" s="19" t="n"/>
     </row>
     <row r="33" ht="76.5" customFormat="1" customHeight="1" s="35">
-      <c r="A33" s="111" t="n"/>
-      <c r="B33" s="111" t="n"/>
-      <c r="C33" s="111" t="n"/>
-      <c r="D33" s="111" t="n"/>
-      <c r="E33" s="111" t="n"/>
-      <c r="F33" s="111" t="n"/>
-      <c r="G33" s="111" t="n"/>
-      <c r="H33" s="111" t="n"/>
       <c r="I33" s="15" t="inlineStr">
         <is>
           <t>Other</t>
@@ -2718,9 +2618,9 @@
       <c r="D35" s="60" t="n">
         <v>1976199</v>
       </c>
-      <c r="E35" s="115" t="n"/>
-      <c r="F35" s="115" t="n"/>
-      <c r="G35" s="115" t="n"/>
+      <c r="E35" s="113" t="n"/>
+      <c r="F35" s="113" t="n"/>
+      <c r="G35" s="113" t="n"/>
       <c r="H35" s="60" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -3250,25 +3150,7 @@
       <c r="X46" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="C26:C31"/>
-    <mergeCell ref="D26:D31"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="A26:A31"/>
-    <mergeCell ref="D2:D10"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="A2:A10"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B2:B10"/>
-    <mergeCell ref="C2:C10"/>
-  </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q35" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -3295,12 +3177,6 @@
     </dataValidation>
     <dataValidation sqref="S2:S35" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
@@ -3429,20 +3305,20 @@
       <c r="T1" s="10" t="n"/>
     </row>
     <row r="2" ht="72.75" customHeight="1">
-      <c r="A2" s="116" t="n">
+      <c r="A2" s="114" t="n">
         <v>126434</v>
       </c>
-      <c r="B2" s="116" t="inlineStr">
+      <c r="B2" s="114" t="inlineStr">
         <is>
           <t>Accel. Clean Energy Access to Reduce Inequality (ACCESS)</t>
         </is>
       </c>
-      <c r="C2" s="117" t="inlineStr">
+      <c r="C2" s="115" t="inlineStr">
         <is>
           <t>http://open.undp.org/projects/00126434</t>
         </is>
       </c>
-      <c r="D2" s="116" t="n">
+      <c r="D2" s="114" t="n">
         <v>15028509</v>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -3475,7 +3351,7 @@
 </t>
         </is>
       </c>
-      <c r="J2" s="118" t="inlineStr">
+      <c r="J2" s="116" t="inlineStr">
         <is>
           <t>KOICA</t>
         </is>
@@ -3497,10 +3373,10 @@
       </c>
     </row>
     <row r="3" ht="57.95" customHeight="1">
-      <c r="A3" s="119" t="n"/>
-      <c r="B3" s="119" t="n"/>
-      <c r="C3" s="119" t="n"/>
-      <c r="D3" s="119" t="n"/>
+      <c r="A3" s="117" t="n"/>
+      <c r="B3" s="117" t="n"/>
+      <c r="C3" s="117" t="n"/>
+      <c r="D3" s="117" t="n"/>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Capacity Training</t>
@@ -3524,7 +3400,7 @@
           <t>achieved – 50 (46% women)</t>
         </is>
       </c>
-      <c r="J3" s="119" t="n"/>
+      <c r="J3" s="117" t="n"/>
       <c r="K3" s="11" t="n">
         <v>0.3</v>
       </c>
@@ -3545,10 +3421,10 @@
       </c>
     </row>
     <row r="4" ht="57.95" customHeight="1">
-      <c r="A4" s="119" t="n"/>
-      <c r="B4" s="119" t="n"/>
-      <c r="C4" s="119" t="n"/>
-      <c r="D4" s="119" t="n"/>
+      <c r="A4" s="117" t="n"/>
+      <c r="B4" s="117" t="n"/>
+      <c r="C4" s="117" t="n"/>
+      <c r="D4" s="117" t="n"/>
       <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
@@ -3572,7 +3448,7 @@
           <t xml:space="preserve">21 </t>
         </is>
       </c>
-      <c r="J4" s="119" t="n"/>
+      <c r="J4" s="117" t="n"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -3590,10 +3466,10 @@
       </c>
     </row>
     <row r="5" ht="57.95" customHeight="1">
-      <c r="A5" s="120" t="n"/>
-      <c r="B5" s="120" t="n"/>
-      <c r="C5" s="120" t="n"/>
-      <c r="D5" s="120" t="n"/>
+      <c r="A5" s="118" t="n"/>
+      <c r="B5" s="118" t="n"/>
+      <c r="C5" s="118" t="n"/>
+      <c r="D5" s="118" t="n"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
@@ -3617,7 +3493,7 @@
           <t>663</t>
         </is>
       </c>
-      <c r="J5" s="120" t="n"/>
+      <c r="J5" s="118" t="n"/>
       <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -3635,20 +3511,20 @@
       </c>
     </row>
     <row r="6" ht="57.95" customHeight="1">
-      <c r="A6" s="116" t="n">
+      <c r="A6" s="114" t="n">
         <v>142434</v>
       </c>
-      <c r="B6" s="116" t="inlineStr">
+      <c r="B6" s="114" t="inlineStr">
         <is>
           <t>PIP Accelerating Robust Carbon Pricing</t>
         </is>
       </c>
-      <c r="C6" s="117" t="inlineStr">
+      <c r="C6" s="115" t="inlineStr">
         <is>
           <t>http://open.undp.org/projects/00142434</t>
         </is>
       </c>
-      <c r="D6" s="116" t="n">
+      <c r="D6" s="114" t="n">
         <v>1796132</v>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -3671,7 +3547,7 @@
         <v>10</v>
       </c>
       <c r="I6" s="1" t="n"/>
-      <c r="J6" s="116" t="inlineStr">
+      <c r="J6" s="114" t="inlineStr">
         <is>
           <t>JSB</t>
         </is>
@@ -3693,10 +3569,10 @@
       </c>
     </row>
     <row r="7" ht="57.95" customHeight="1">
-      <c r="A7" s="119" t="n"/>
-      <c r="B7" s="119" t="n"/>
-      <c r="C7" s="119" t="n"/>
-      <c r="D7" s="119" t="n"/>
+      <c r="A7" s="117" t="n"/>
+      <c r="B7" s="117" t="n"/>
+      <c r="C7" s="117" t="n"/>
+      <c r="D7" s="117" t="n"/>
       <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
@@ -3716,7 +3592,7 @@
         <v>329</v>
       </c>
       <c r="I7" s="1" t="n"/>
-      <c r="J7" s="119" t="n"/>
+      <c r="J7" s="117" t="n"/>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -3744,10 +3620,10 @@
       </c>
     </row>
     <row r="8" ht="57.95" customHeight="1">
-      <c r="A8" s="120" t="n"/>
-      <c r="B8" s="120" t="n"/>
-      <c r="C8" s="120" t="n"/>
-      <c r="D8" s="120" t="n"/>
+      <c r="A8" s="118" t="n"/>
+      <c r="B8" s="118" t="n"/>
+      <c r="C8" s="118" t="n"/>
+      <c r="D8" s="118" t="n"/>
       <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Capacity Training</t>
@@ -3767,7 +3643,7 @@
         <v>350</v>
       </c>
       <c r="I8" s="1" t="n"/>
-      <c r="J8" s="120" t="n"/>
+      <c r="J8" s="118" t="n"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -3841,20 +3717,20 @@
       </c>
     </row>
     <row r="10" ht="87" customHeight="1">
-      <c r="A10" s="116" t="n">
+      <c r="A10" s="114" t="n">
         <v>5721</v>
       </c>
-      <c r="B10" s="116" t="inlineStr">
+      <c r="B10" s="114" t="inlineStr">
         <is>
           <t>ADLIGHT</t>
         </is>
       </c>
-      <c r="C10" s="116" t="inlineStr">
+      <c r="C10" s="114" t="inlineStr">
         <is>
           <t>PIMS+</t>
         </is>
       </c>
-      <c r="D10" s="116" t="n">
+      <c r="D10" s="114" t="n">
         <v>2633372</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -3879,7 +3755,7 @@
         <v>125</v>
       </c>
       <c r="I10" s="1" t="n"/>
-      <c r="J10" s="116" t="inlineStr">
+      <c r="J10" s="114" t="inlineStr">
         <is>
           <t>GEF</t>
         </is>
@@ -3904,10 +3780,10 @@
       </c>
     </row>
     <row r="11" ht="57.95" customHeight="1">
-      <c r="A11" s="120" t="n"/>
-      <c r="B11" s="120" t="n"/>
-      <c r="C11" s="120" t="n"/>
-      <c r="D11" s="120" t="n"/>
+      <c r="A11" s="118" t="n"/>
+      <c r="B11" s="118" t="n"/>
+      <c r="C11" s="118" t="n"/>
+      <c r="D11" s="118" t="n"/>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
@@ -3927,7 +3803,7 @@
         <v>10</v>
       </c>
       <c r="I11" s="1" t="n"/>
-      <c r="J11" s="120" t="n"/>
+      <c r="J11" s="118" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
           <t>VF</t>
@@ -4131,23 +4007,23 @@
       </c>
     </row>
     <row r="2" ht="72.75" customHeight="1">
-      <c r="A2" s="116" t="n">
+      <c r="A2" s="114" t="n">
         <v>126434</v>
       </c>
-      <c r="B2" s="116" t="inlineStr">
+      <c r="B2" s="114" t="inlineStr">
         <is>
           <t>Accel. Clean Energy Access to Reduce Inequality (ACCESS)</t>
         </is>
       </c>
-      <c r="C2" s="117" t="inlineStr">
+      <c r="C2" s="115" t="inlineStr">
         <is>
           <t>http://open.undp.org/projects/00126434</t>
         </is>
       </c>
-      <c r="D2" s="116" t="n">
+      <c r="D2" s="114" t="n">
         <v>15028509</v>
       </c>
-      <c r="E2" s="118" t="inlineStr">
+      <c r="E2" s="116" t="inlineStr">
         <is>
           <t>KOICA</t>
         </is>
@@ -4189,11 +4065,11 @@
       </c>
     </row>
     <row r="3" ht="29.1" customHeight="1">
-      <c r="A3" s="119" t="n"/>
-      <c r="B3" s="119" t="n"/>
-      <c r="C3" s="119" t="n"/>
-      <c r="D3" s="119" t="n"/>
-      <c r="E3" s="119" t="n"/>
+      <c r="A3" s="117" t="n"/>
+      <c r="B3" s="117" t="n"/>
+      <c r="C3" s="117" t="n"/>
+      <c r="D3" s="117" t="n"/>
+      <c r="E3" s="117" t="n"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Capacity Training</t>
@@ -4221,11 +4097,11 @@
       </c>
     </row>
     <row r="4" ht="29.1" customHeight="1">
-      <c r="A4" s="119" t="n"/>
-      <c r="B4" s="119" t="n"/>
-      <c r="C4" s="119" t="n"/>
-      <c r="D4" s="119" t="n"/>
-      <c r="E4" s="119" t="n"/>
+      <c r="A4" s="117" t="n"/>
+      <c r="B4" s="117" t="n"/>
+      <c r="C4" s="117" t="n"/>
+      <c r="D4" s="117" t="n"/>
+      <c r="E4" s="117" t="n"/>
       <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
@@ -4253,11 +4129,11 @@
       </c>
     </row>
     <row r="5" ht="43.5" customHeight="1">
-      <c r="A5" s="120" t="n"/>
-      <c r="B5" s="120" t="n"/>
-      <c r="C5" s="120" t="n"/>
-      <c r="D5" s="120" t="n"/>
-      <c r="E5" s="120" t="n"/>
+      <c r="A5" s="118" t="n"/>
+      <c r="B5" s="118" t="n"/>
+      <c r="C5" s="118" t="n"/>
+      <c r="D5" s="118" t="n"/>
+      <c r="E5" s="118" t="n"/>
       <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
@@ -4285,23 +4161,23 @@
       </c>
     </row>
     <row r="6" ht="43.5" customHeight="1">
-      <c r="A6" s="116" t="n">
+      <c r="A6" s="114" t="n">
         <v>142434</v>
       </c>
-      <c r="B6" s="116" t="inlineStr">
+      <c r="B6" s="114" t="inlineStr">
         <is>
           <t>PIP Accelerating Robust Carbon Pricing</t>
         </is>
       </c>
-      <c r="C6" s="117" t="inlineStr">
+      <c r="C6" s="115" t="inlineStr">
         <is>
           <t>http://open.undp.org/projects/00142434</t>
         </is>
       </c>
-      <c r="D6" s="116" t="n">
+      <c r="D6" s="114" t="n">
         <v>1796132</v>
       </c>
-      <c r="E6" s="116" t="inlineStr">
+      <c r="E6" s="114" t="inlineStr">
         <is>
           <t>JSB</t>
         </is>
@@ -4330,11 +4206,11 @@
       <c r="J6" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="119" t="n"/>
-      <c r="B7" s="119" t="n"/>
-      <c r="C7" s="119" t="n"/>
-      <c r="D7" s="119" t="n"/>
-      <c r="E7" s="119" t="n"/>
+      <c r="A7" s="117" t="n"/>
+      <c r="B7" s="117" t="n"/>
+      <c r="C7" s="117" t="n"/>
+      <c r="D7" s="117" t="n"/>
+      <c r="E7" s="117" t="n"/>
       <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
@@ -4358,11 +4234,11 @@
       <c r="J7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="120" t="n"/>
-      <c r="B8" s="120" t="n"/>
-      <c r="C8" s="120" t="n"/>
-      <c r="D8" s="120" t="n"/>
-      <c r="E8" s="120" t="n"/>
+      <c r="A8" s="118" t="n"/>
+      <c r="B8" s="118" t="n"/>
+      <c r="C8" s="118" t="n"/>
+      <c r="D8" s="118" t="n"/>
+      <c r="E8" s="118" t="n"/>
       <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Capacity Training</t>
@@ -4433,23 +4309,23 @@
       <c r="J9" s="1" t="n"/>
     </row>
     <row r="10" ht="87" customHeight="1">
-      <c r="A10" s="116" t="n">
+      <c r="A10" s="114" t="n">
         <v>5721</v>
       </c>
-      <c r="B10" s="116" t="inlineStr">
+      <c r="B10" s="114" t="inlineStr">
         <is>
           <t>ADLIGHT</t>
         </is>
       </c>
-      <c r="C10" s="116" t="inlineStr">
+      <c r="C10" s="114" t="inlineStr">
         <is>
           <t>PIMS+</t>
         </is>
       </c>
-      <c r="D10" s="116" t="n">
+      <c r="D10" s="114" t="n">
         <v>2633372</v>
       </c>
-      <c r="E10" s="116" t="inlineStr">
+      <c r="E10" s="114" t="inlineStr">
         <is>
           <t>GEF</t>
         </is>
@@ -4481,11 +4357,11 @@
       <c r="J10" s="1" t="n"/>
     </row>
     <row r="11" ht="29.1" customHeight="1">
-      <c r="A11" s="120" t="n"/>
-      <c r="B11" s="120" t="n"/>
-      <c r="C11" s="120" t="n"/>
-      <c r="D11" s="120" t="n"/>
-      <c r="E11" s="120" t="n"/>
+      <c r="A11" s="118" t="n"/>
+      <c r="B11" s="118" t="n"/>
+      <c r="C11" s="118" t="n"/>
+      <c r="D11" s="118" t="n"/>
+      <c r="E11" s="118" t="n"/>
       <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
@@ -4599,12 +4475,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="121" t="inlineStr">
+      <c r="A1" s="119" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="121" t="inlineStr">
+      <c r="B1" s="119" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
